--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592208</v>
+        <v>121592210</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594557</v>
+        <v>594660</v>
       </c>
       <c r="R2" t="n">
-        <v>7185802</v>
+        <v>7185655</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592207</v>
+        <v>121592190</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594451</v>
+        <v>594270</v>
       </c>
       <c r="R3" t="n">
-        <v>7185924</v>
+        <v>7185863</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592194</v>
+        <v>121592192</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>74720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,7 +947,7 @@
         <v>594293</v>
       </c>
       <c r="R4" t="n">
-        <v>7185909</v>
+        <v>7185910</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592188</v>
+        <v>121592219</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594365</v>
+        <v>594709</v>
       </c>
       <c r="R5" t="n">
-        <v>7185581</v>
+        <v>7185499</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592193</v>
+        <v>121592203</v>
       </c>
       <c r="B6" t="n">
-        <v>74699</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,38 +1140,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594293</v>
+        <v>594461</v>
       </c>
       <c r="R6" t="n">
-        <v>7185910</v>
+        <v>7185985</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592219</v>
+        <v>121592211</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1275,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594709</v>
+        <v>594658</v>
       </c>
       <c r="R7" t="n">
-        <v>7185499</v>
+        <v>7185656</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592220</v>
+        <v>121592193</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>74699</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,43 +1369,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594604</v>
+        <v>594293</v>
       </c>
       <c r="R8" t="n">
-        <v>7185461</v>
+        <v>7185910</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592210</v>
+        <v>121592220</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1500,7 +1505,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1509,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594660</v>
+        <v>594604</v>
       </c>
       <c r="R9" t="n">
-        <v>7185655</v>
+        <v>7185461</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592205</v>
+        <v>121592188</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594475</v>
+        <v>594365</v>
       </c>
       <c r="R10" t="n">
-        <v>7185979</v>
+        <v>7185581</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592213</v>
+        <v>121592202</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,34 +1714,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594681</v>
+        <v>594480</v>
       </c>
       <c r="R11" t="n">
-        <v>7185598</v>
+        <v>7186028</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592203</v>
+        <v>121592207</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594461</v>
+        <v>594451</v>
       </c>
       <c r="R12" t="n">
-        <v>7185985</v>
+        <v>7185924</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592192</v>
+        <v>121592208</v>
       </c>
       <c r="B13" t="n">
-        <v>74720</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1943,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594293</v>
+        <v>594557</v>
       </c>
       <c r="R13" t="n">
-        <v>7185910</v>
+        <v>7185802</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592190</v>
+        <v>121592189</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,21 +2055,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594270</v>
+        <v>594269</v>
       </c>
       <c r="R14" t="n">
-        <v>7185863</v>
+        <v>7185866</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2146,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592187</v>
+        <v>121592212</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,16 +2167,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2182,7 +2187,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2191,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594367</v>
+        <v>594673</v>
       </c>
       <c r="R15" t="n">
-        <v>7185583</v>
+        <v>7185646</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592211</v>
+        <v>121592222</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,34 +2284,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594658</v>
+        <v>594343</v>
       </c>
       <c r="R16" t="n">
-        <v>7185656</v>
+        <v>7185457</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2338,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592189</v>
+        <v>121592187</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,34 +2401,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594269</v>
+        <v>594367</v>
       </c>
       <c r="R17" t="n">
-        <v>7185866</v>
+        <v>7185583</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2475,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2502,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592222</v>
+        <v>121592194</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,39 +2518,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594343</v>
+        <v>594293</v>
       </c>
       <c r="R18" t="n">
-        <v>7185457</v>
+        <v>7185909</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2577,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2587,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592212</v>
+        <v>121592213</v>
       </c>
       <c r="B19" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,39 +2630,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594673</v>
+        <v>594681</v>
       </c>
       <c r="R19" t="n">
-        <v>7185646</v>
+        <v>7185598</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2684,7 +2689,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2694,7 +2699,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,10 +2726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592202</v>
+        <v>121592205</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,39 +2742,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594480</v>
+        <v>594475</v>
       </c>
       <c r="R20" t="n">
-        <v>7186028</v>
+        <v>7185979</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592210</v>
+        <v>121592187</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594660</v>
+        <v>594367</v>
       </c>
       <c r="R2" t="n">
-        <v>7185655</v>
+        <v>7185583</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592190</v>
+        <v>121592208</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594270</v>
+        <v>594557</v>
       </c>
       <c r="R3" t="n">
-        <v>7185863</v>
+        <v>7185802</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592192</v>
+        <v>121592222</v>
       </c>
       <c r="B4" t="n">
-        <v>74720</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594293</v>
+        <v>594343</v>
       </c>
       <c r="R4" t="n">
-        <v>7185910</v>
+        <v>7185457</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592219</v>
+        <v>121592203</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594709</v>
+        <v>594461</v>
       </c>
       <c r="R5" t="n">
-        <v>7185499</v>
+        <v>7185985</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592203</v>
+        <v>121592205</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594461</v>
+        <v>594475</v>
       </c>
       <c r="R6" t="n">
-        <v>7185985</v>
+        <v>7185979</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592211</v>
+        <v>121592192</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>74720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594658</v>
+        <v>594293</v>
       </c>
       <c r="R7" t="n">
-        <v>7185656</v>
+        <v>7185910</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592193</v>
+        <v>121592211</v>
       </c>
       <c r="B8" t="n">
-        <v>74699</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594293</v>
+        <v>594658</v>
       </c>
       <c r="R8" t="n">
-        <v>7185910</v>
+        <v>7185656</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592220</v>
+        <v>121592188</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,39 +1490,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594604</v>
+        <v>594365</v>
       </c>
       <c r="R9" t="n">
-        <v>7185461</v>
+        <v>7185581</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592188</v>
+        <v>121592212</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,34 +1602,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594365</v>
+        <v>594673</v>
       </c>
       <c r="R10" t="n">
-        <v>7185581</v>
+        <v>7185646</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592202</v>
+        <v>121592219</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,39 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594480</v>
+        <v>594709</v>
       </c>
       <c r="R11" t="n">
-        <v>7186028</v>
+        <v>7185499</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592207</v>
+        <v>121592202</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,34 +1831,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594451</v>
+        <v>594480</v>
       </c>
       <c r="R12" t="n">
-        <v>7185924</v>
+        <v>7186028</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,7 +1932,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592208</v>
+        <v>121592190</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1967,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594557</v>
+        <v>594270</v>
       </c>
       <c r="R13" t="n">
-        <v>7185802</v>
+        <v>7185863</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592189</v>
+        <v>121592207</v>
       </c>
       <c r="B14" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,21 +2060,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2079,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594269</v>
+        <v>594451</v>
       </c>
       <c r="R14" t="n">
-        <v>7185866</v>
+        <v>7185924</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592212</v>
+        <v>121592189</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,39 +2172,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594673</v>
+        <v>594269</v>
       </c>
       <c r="R15" t="n">
-        <v>7185646</v>
+        <v>7185866</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,7 +2268,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592222</v>
+        <v>121592210</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594343</v>
+        <v>594660</v>
       </c>
       <c r="R16" t="n">
-        <v>7185457</v>
+        <v>7185655</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,7 +2385,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592187</v>
+        <v>121592220</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2421,7 +2421,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594367</v>
+        <v>594604</v>
       </c>
       <c r="R17" t="n">
-        <v>7185583</v>
+        <v>7185461</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,10 +2502,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592194</v>
+        <v>121592193</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>74699</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,25 +2514,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
         <v>594293</v>
       </c>
       <c r="R18" t="n">
-        <v>7185909</v>
+        <v>7185910</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592205</v>
+        <v>121592194</v>
       </c>
       <c r="B20" t="n">
         <v>78609</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594475</v>
+        <v>594293</v>
       </c>
       <c r="R20" t="n">
-        <v>7185979</v>
+        <v>7185909</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592187</v>
+        <v>121592193</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>74699</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594367</v>
+        <v>594293</v>
       </c>
       <c r="R2" t="n">
-        <v>7185583</v>
+        <v>7185910</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592208</v>
+        <v>121592187</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594557</v>
+        <v>594367</v>
       </c>
       <c r="R3" t="n">
-        <v>7185802</v>
+        <v>7185583</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592222</v>
+        <v>121592205</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594343</v>
+        <v>594475</v>
       </c>
       <c r="R4" t="n">
-        <v>7185457</v>
+        <v>7185979</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592203</v>
+        <v>121592212</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1057,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594461</v>
+        <v>594673</v>
       </c>
       <c r="R5" t="n">
-        <v>7185985</v>
+        <v>7185646</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592205</v>
+        <v>121592210</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594475</v>
+        <v>594660</v>
       </c>
       <c r="R6" t="n">
-        <v>7185979</v>
+        <v>7185655</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592192</v>
+        <v>121592220</v>
       </c>
       <c r="B7" t="n">
-        <v>74720</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594293</v>
+        <v>594604</v>
       </c>
       <c r="R7" t="n">
-        <v>7185910</v>
+        <v>7185461</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592211</v>
+        <v>121592189</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594658</v>
+        <v>594269</v>
       </c>
       <c r="R8" t="n">
-        <v>7185656</v>
+        <v>7185866</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592188</v>
+        <v>121592190</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1514,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594365</v>
+        <v>594270</v>
       </c>
       <c r="R9" t="n">
-        <v>7185581</v>
+        <v>7185863</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592212</v>
+        <v>121592207</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,39 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594673</v>
+        <v>594451</v>
       </c>
       <c r="R10" t="n">
-        <v>7185646</v>
+        <v>7185924</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592219</v>
+        <v>121592194</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594709</v>
+        <v>594293</v>
       </c>
       <c r="R11" t="n">
-        <v>7185499</v>
+        <v>7185909</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592202</v>
+        <v>121592211</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594480</v>
+        <v>594658</v>
       </c>
       <c r="R12" t="n">
-        <v>7186028</v>
+        <v>7185656</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592190</v>
+        <v>121592222</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,34 +1943,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594270</v>
+        <v>594343</v>
       </c>
       <c r="R13" t="n">
-        <v>7185863</v>
+        <v>7185457</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,7 +2044,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592207</v>
+        <v>121592188</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594451</v>
+        <v>594365</v>
       </c>
       <c r="R14" t="n">
-        <v>7185924</v>
+        <v>7185581</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592189</v>
+        <v>121592213</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594269</v>
+        <v>594681</v>
       </c>
       <c r="R15" t="n">
-        <v>7185866</v>
+        <v>7185598</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592210</v>
+        <v>121592192</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>74720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,39 +2284,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594660</v>
+        <v>594293</v>
       </c>
       <c r="R16" t="n">
-        <v>7185655</v>
+        <v>7185910</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,7 +2380,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592220</v>
+        <v>121592202</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2421,7 +2416,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2430,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594604</v>
+        <v>594480</v>
       </c>
       <c r="R17" t="n">
-        <v>7185461</v>
+        <v>7186028</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2465,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592193</v>
+        <v>121592208</v>
       </c>
       <c r="B18" t="n">
-        <v>74699</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,25 +2509,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2542,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594293</v>
+        <v>594557</v>
       </c>
       <c r="R18" t="n">
-        <v>7185910</v>
+        <v>7185802</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2577,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,7 +2609,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592213</v>
+        <v>121592219</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2654,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594681</v>
+        <v>594709</v>
       </c>
       <c r="R19" t="n">
-        <v>7185598</v>
+        <v>7185499</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2689,7 +2684,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2699,7 +2694,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,10 +2721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592194</v>
+        <v>121592203</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,34 +2737,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594293</v>
+        <v>594461</v>
       </c>
       <c r="R20" t="n">
-        <v>7185909</v>
+        <v>7185985</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592193</v>
+        <v>121592188</v>
       </c>
       <c r="B2" t="n">
-        <v>74699</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594293</v>
+        <v>594365</v>
       </c>
       <c r="R2" t="n">
-        <v>7185910</v>
+        <v>7185581</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592187</v>
+        <v>121592189</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594367</v>
+        <v>594269</v>
       </c>
       <c r="R3" t="n">
-        <v>7185583</v>
+        <v>7185866</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592205</v>
+        <v>121592210</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594475</v>
+        <v>594660</v>
       </c>
       <c r="R4" t="n">
-        <v>7185979</v>
+        <v>7185655</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592210</v>
+        <v>121592213</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594660</v>
+        <v>594681</v>
       </c>
       <c r="R6" t="n">
-        <v>7185655</v>
+        <v>7185598</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592220</v>
+        <v>121592194</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594604</v>
+        <v>594293</v>
       </c>
       <c r="R7" t="n">
-        <v>7185461</v>
+        <v>7185909</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592189</v>
+        <v>121592219</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594269</v>
+        <v>594709</v>
       </c>
       <c r="R8" t="n">
-        <v>7185866</v>
+        <v>7185499</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592190</v>
+        <v>121592202</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,34 +1485,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594270</v>
+        <v>594480</v>
       </c>
       <c r="R9" t="n">
-        <v>7185863</v>
+        <v>7186028</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,7 +1698,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592194</v>
+        <v>121592205</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1743,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594293</v>
+        <v>594475</v>
       </c>
       <c r="R11" t="n">
-        <v>7185909</v>
+        <v>7185979</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,7 +1810,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592211</v>
+        <v>121592190</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1855,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594658</v>
+        <v>594270</v>
       </c>
       <c r="R12" t="n">
-        <v>7185656</v>
+        <v>7185863</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592222</v>
+        <v>121592208</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,39 +1938,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594343</v>
+        <v>594557</v>
       </c>
       <c r="R13" t="n">
-        <v>7185457</v>
+        <v>7185802</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,7 +2034,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592188</v>
+        <v>121592211</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -2084,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594365</v>
+        <v>594658</v>
       </c>
       <c r="R14" t="n">
-        <v>7185581</v>
+        <v>7185656</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592213</v>
+        <v>121592193</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>74699</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,25 +2158,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594681</v>
+        <v>594293</v>
       </c>
       <c r="R15" t="n">
-        <v>7185598</v>
+        <v>7185910</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592192</v>
+        <v>121592222</v>
       </c>
       <c r="B16" t="n">
-        <v>74720</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,34 +2274,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594293</v>
+        <v>594343</v>
       </c>
       <c r="R16" t="n">
-        <v>7185910</v>
+        <v>7185457</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,7 +2375,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592202</v>
+        <v>121592220</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2416,7 +2411,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2425,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594480</v>
+        <v>594604</v>
       </c>
       <c r="R17" t="n">
-        <v>7186028</v>
+        <v>7185461</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592208</v>
+        <v>121592192</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>74720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,21 +2508,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2537,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594557</v>
+        <v>594293</v>
       </c>
       <c r="R18" t="n">
-        <v>7185802</v>
+        <v>7185910</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592219</v>
+        <v>121592187</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,34 +2620,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594709</v>
+        <v>594367</v>
       </c>
       <c r="R19" t="n">
-        <v>7185499</v>
+        <v>7185583</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592213</v>
+        <v>121592219</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594681</v>
+        <v>594709</v>
       </c>
       <c r="R2" t="n">
-        <v>7185598</v>
+        <v>7185499</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592211</v>
+        <v>121592187</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594658</v>
+        <v>594367</v>
       </c>
       <c r="R3" t="n">
-        <v>7185656</v>
+        <v>7185583</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592207</v>
+        <v>121592210</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594451</v>
+        <v>594660</v>
       </c>
       <c r="R4" t="n">
-        <v>7185924</v>
+        <v>7185655</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592194</v>
+        <v>121592203</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594293</v>
+        <v>594461</v>
       </c>
       <c r="R5" t="n">
-        <v>7185909</v>
+        <v>7185985</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592188</v>
+        <v>121592208</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1163,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594365</v>
+        <v>594557</v>
       </c>
       <c r="R6" t="n">
-        <v>7185581</v>
+        <v>7185802</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592205</v>
+        <v>121592202</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594475</v>
+        <v>594480</v>
       </c>
       <c r="R7" t="n">
-        <v>7185979</v>
+        <v>7186028</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592219</v>
+        <v>121592192</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>74727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594709</v>
+        <v>594293</v>
       </c>
       <c r="R8" t="n">
-        <v>7185499</v>
+        <v>7185910</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592189</v>
+        <v>121592205</v>
       </c>
       <c r="B9" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594269</v>
+        <v>594475</v>
       </c>
       <c r="R9" t="n">
-        <v>7185866</v>
+        <v>7185979</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592220</v>
+        <v>121592189</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,39 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594604</v>
+        <v>594269</v>
       </c>
       <c r="R10" t="n">
-        <v>7185461</v>
+        <v>7185866</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592208</v>
+        <v>121592212</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,34 +1719,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594557</v>
+        <v>594673</v>
       </c>
       <c r="R11" t="n">
-        <v>7185802</v>
+        <v>7185646</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592190</v>
+        <v>121592220</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,34 +1836,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594270</v>
+        <v>594604</v>
       </c>
       <c r="R12" t="n">
-        <v>7185863</v>
+        <v>7185461</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592193</v>
+        <v>121592211</v>
       </c>
       <c r="B13" t="n">
-        <v>74706</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,25 +1949,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594293</v>
+        <v>594658</v>
       </c>
       <c r="R13" t="n">
-        <v>7185910</v>
+        <v>7185656</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592202</v>
+        <v>121592194</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,39 +2065,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594480</v>
+        <v>594293</v>
       </c>
       <c r="R14" t="n">
-        <v>7186028</v>
+        <v>7185909</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592192</v>
+        <v>121592213</v>
       </c>
       <c r="B15" t="n">
-        <v>74727</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2177,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594293</v>
+        <v>594681</v>
       </c>
       <c r="R15" t="n">
-        <v>7185910</v>
+        <v>7185598</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592203</v>
+        <v>121592207</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,39 +2289,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594461</v>
+        <v>594451</v>
       </c>
       <c r="R16" t="n">
-        <v>7185985</v>
+        <v>7185924</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592210</v>
+        <v>121592193</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>74706</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2382,43 +2397,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594660</v>
+        <v>594293</v>
       </c>
       <c r="R17" t="n">
-        <v>7185655</v>
+        <v>7185910</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592222</v>
+        <v>121592190</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,39 +2513,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594343</v>
+        <v>594270</v>
       </c>
       <c r="R18" t="n">
-        <v>7185457</v>
+        <v>7185863</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2609,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592187</v>
+        <v>121592188</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,39 +2625,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594367</v>
+        <v>594365</v>
       </c>
       <c r="R19" t="n">
-        <v>7185583</v>
+        <v>7185581</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2721,10 +2721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592212</v>
+        <v>121592222</v>
       </c>
       <c r="B20" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2757,7 +2757,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594673</v>
+        <v>594343</v>
       </c>
       <c r="R20" t="n">
-        <v>7185646</v>
+        <v>7185457</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592208</v>
+        <v>121592202</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594557</v>
+        <v>594480</v>
       </c>
       <c r="R6" t="n">
-        <v>7185802</v>
+        <v>7186028</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592202</v>
+        <v>121592208</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594480</v>
+        <v>594557</v>
       </c>
       <c r="R7" t="n">
-        <v>7186028</v>
+        <v>7185802</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592219</v>
+        <v>121592203</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594709</v>
+        <v>594461</v>
       </c>
       <c r="R2" t="n">
-        <v>7185499</v>
+        <v>7185985</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592187</v>
+        <v>121592189</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594367</v>
+        <v>594269</v>
       </c>
       <c r="R3" t="n">
-        <v>7185583</v>
+        <v>7185866</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592210</v>
+        <v>121592219</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594660</v>
+        <v>594709</v>
       </c>
       <c r="R4" t="n">
-        <v>7185655</v>
+        <v>7185499</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592203</v>
+        <v>121592213</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594461</v>
+        <v>594681</v>
       </c>
       <c r="R5" t="n">
-        <v>7185985</v>
+        <v>7185598</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592202</v>
+        <v>121592210</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1183,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594480</v>
+        <v>594660</v>
       </c>
       <c r="R6" t="n">
-        <v>7186028</v>
+        <v>7185655</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592208</v>
+        <v>121592207</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1295,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594557</v>
+        <v>594451</v>
       </c>
       <c r="R7" t="n">
-        <v>7185802</v>
+        <v>7185924</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592192</v>
+        <v>121592188</v>
       </c>
       <c r="B8" t="n">
-        <v>74727</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594293</v>
+        <v>594365</v>
       </c>
       <c r="R8" t="n">
-        <v>7185910</v>
+        <v>7185581</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592205</v>
+        <v>121592208</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1519,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594475</v>
+        <v>594557</v>
       </c>
       <c r="R9" t="n">
-        <v>7185979</v>
+        <v>7185802</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592189</v>
+        <v>121592212</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,34 +1597,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594269</v>
+        <v>594673</v>
       </c>
       <c r="R10" t="n">
-        <v>7185866</v>
+        <v>7185646</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592212</v>
+        <v>121592220</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,16 +1714,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1748,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594673</v>
+        <v>594604</v>
       </c>
       <c r="R11" t="n">
-        <v>7185646</v>
+        <v>7185461</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1783,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592220</v>
+        <v>121592194</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594604</v>
+        <v>594293</v>
       </c>
       <c r="R12" t="n">
-        <v>7185461</v>
+        <v>7185909</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1900,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592211</v>
+        <v>121592202</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,34 +1943,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594658</v>
+        <v>594480</v>
       </c>
       <c r="R13" t="n">
-        <v>7185656</v>
+        <v>7186028</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2012,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592194</v>
+        <v>121592192</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>74727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,21 +2060,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,7 +2087,7 @@
         <v>594293</v>
       </c>
       <c r="R14" t="n">
-        <v>7185909</v>
+        <v>7185910</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2161,7 +2156,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592213</v>
+        <v>121592190</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2201,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594681</v>
+        <v>594270</v>
       </c>
       <c r="R15" t="n">
-        <v>7185598</v>
+        <v>7185863</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2236,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592207</v>
+        <v>121592193</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>74706</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,25 +2280,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2313,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594451</v>
+        <v>594293</v>
       </c>
       <c r="R16" t="n">
-        <v>7185924</v>
+        <v>7185910</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592193</v>
+        <v>121592187</v>
       </c>
       <c r="B17" t="n">
-        <v>74706</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,38 +2392,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594293</v>
+        <v>594367</v>
       </c>
       <c r="R17" t="n">
-        <v>7185910</v>
+        <v>7185583</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,7 +2497,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592190</v>
+        <v>121592211</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594270</v>
+        <v>594658</v>
       </c>
       <c r="R18" t="n">
-        <v>7185863</v>
+        <v>7185656</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,10 +2609,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592188</v>
+        <v>121592222</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,34 +2625,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594365</v>
+        <v>594343</v>
       </c>
       <c r="R19" t="n">
-        <v>7185581</v>
+        <v>7185457</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2684,7 +2689,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2694,7 +2699,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,10 +2726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592222</v>
+        <v>121592205</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,39 +2742,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594343</v>
+        <v>594475</v>
       </c>
       <c r="R20" t="n">
-        <v>7185457</v>
+        <v>7185979</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592202</v>
+        <v>121592190</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,39 +1943,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594480</v>
+        <v>594270</v>
       </c>
       <c r="R13" t="n">
-        <v>7186028</v>
+        <v>7185863</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2156,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592190</v>
+        <v>121592202</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,34 +2167,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594270</v>
+        <v>594480</v>
       </c>
       <c r="R15" t="n">
-        <v>7185863</v>
+        <v>7186028</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592203</v>
+        <v>121592202</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594461</v>
+        <v>594480</v>
       </c>
       <c r="R2" t="n">
-        <v>7185985</v>
+        <v>7186028</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592189</v>
+        <v>121592203</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594269</v>
+        <v>594461</v>
       </c>
       <c r="R3" t="n">
-        <v>7185866</v>
+        <v>7185985</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592219</v>
+        <v>121592205</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594709</v>
+        <v>594475</v>
       </c>
       <c r="R4" t="n">
-        <v>7185499</v>
+        <v>7185979</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592213</v>
+        <v>121592187</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594681</v>
+        <v>594367</v>
       </c>
       <c r="R5" t="n">
-        <v>7185598</v>
+        <v>7185583</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592210</v>
+        <v>121592189</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594660</v>
+        <v>594269</v>
       </c>
       <c r="R6" t="n">
-        <v>7185655</v>
+        <v>7185866</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592207</v>
+        <v>121592188</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1285,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594451</v>
+        <v>594365</v>
       </c>
       <c r="R7" t="n">
-        <v>7185924</v>
+        <v>7185581</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592188</v>
+        <v>121592208</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1397,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594365</v>
+        <v>594557</v>
       </c>
       <c r="R8" t="n">
-        <v>7185581</v>
+        <v>7185802</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592208</v>
+        <v>121592222</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,34 +1490,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594557</v>
+        <v>594343</v>
       </c>
       <c r="R9" t="n">
-        <v>7185802</v>
+        <v>7185457</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592212</v>
+        <v>121592210</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,16 +1607,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1617,7 +1627,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1626,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594673</v>
+        <v>594660</v>
       </c>
       <c r="R10" t="n">
-        <v>7185646</v>
+        <v>7185655</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1815,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592194</v>
+        <v>121592190</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1855,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594293</v>
+        <v>594270</v>
       </c>
       <c r="R12" t="n">
-        <v>7185909</v>
+        <v>7185863</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,7 +1937,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592190</v>
+        <v>121592207</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1967,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594270</v>
+        <v>594451</v>
       </c>
       <c r="R13" t="n">
-        <v>7185863</v>
+        <v>7185924</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592192</v>
+        <v>121592219</v>
       </c>
       <c r="B14" t="n">
-        <v>74727</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,21 +2065,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2079,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594293</v>
+        <v>594709</v>
       </c>
       <c r="R14" t="n">
-        <v>7185910</v>
+        <v>7185499</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592202</v>
+        <v>121592213</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,39 +2177,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594480</v>
+        <v>594681</v>
       </c>
       <c r="R15" t="n">
-        <v>7186028</v>
+        <v>7185598</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2380,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592187</v>
+        <v>121592194</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,39 +2401,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594367</v>
+        <v>594293</v>
       </c>
       <c r="R17" t="n">
-        <v>7185583</v>
+        <v>7185909</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592211</v>
+        <v>121592212</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,34 +2513,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594658</v>
+        <v>594673</v>
       </c>
       <c r="R18" t="n">
-        <v>7185656</v>
+        <v>7185646</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2577,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2587,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,10 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592222</v>
+        <v>121592211</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,39 +2630,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594343</v>
+        <v>594658</v>
       </c>
       <c r="R19" t="n">
-        <v>7185457</v>
+        <v>7185656</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,10 +2726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592205</v>
+        <v>121592192</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>74727</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,21 +2742,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594475</v>
+        <v>594293</v>
       </c>
       <c r="R20" t="n">
-        <v>7185979</v>
+        <v>7185910</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592202</v>
+        <v>121592219</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594480</v>
+        <v>594709</v>
       </c>
       <c r="R2" t="n">
-        <v>7186028</v>
+        <v>7185499</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592203</v>
+        <v>121592194</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594461</v>
+        <v>594293</v>
       </c>
       <c r="R3" t="n">
-        <v>7185985</v>
+        <v>7185909</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592205</v>
+        <v>121592208</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594475</v>
+        <v>594557</v>
       </c>
       <c r="R4" t="n">
-        <v>7185979</v>
+        <v>7185802</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1138,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592189</v>
+        <v>121592205</v>
       </c>
       <c r="B6" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594269</v>
+        <v>594475</v>
       </c>
       <c r="R6" t="n">
-        <v>7185866</v>
+        <v>7185979</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592188</v>
+        <v>121592212</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594365</v>
+        <v>594673</v>
       </c>
       <c r="R7" t="n">
-        <v>7185581</v>
+        <v>7185646</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592208</v>
+        <v>121592193</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>74706</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594557</v>
+        <v>594293</v>
       </c>
       <c r="R8" t="n">
-        <v>7185802</v>
+        <v>7185910</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592222</v>
+        <v>121592220</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1510,7 +1505,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1519,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594343</v>
+        <v>594604</v>
       </c>
       <c r="R9" t="n">
-        <v>7185457</v>
+        <v>7185461</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592210</v>
+        <v>121592190</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,39 +1602,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594660</v>
+        <v>594270</v>
       </c>
       <c r="R10" t="n">
-        <v>7185655</v>
+        <v>7185863</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592220</v>
+        <v>121592192</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>74727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,39 +1714,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594604</v>
+        <v>594293</v>
       </c>
       <c r="R11" t="n">
-        <v>7185461</v>
+        <v>7185910</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1788,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,7 +1810,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592190</v>
+        <v>121592207</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1865,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594270</v>
+        <v>594451</v>
       </c>
       <c r="R12" t="n">
-        <v>7185863</v>
+        <v>7185924</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1900,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,7 +1922,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592207</v>
+        <v>121592213</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1977,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594451</v>
+        <v>594681</v>
       </c>
       <c r="R13" t="n">
-        <v>7185924</v>
+        <v>7185598</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2012,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,7 +2034,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592219</v>
+        <v>121592188</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2089,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594709</v>
+        <v>594365</v>
       </c>
       <c r="R14" t="n">
-        <v>7185499</v>
+        <v>7185581</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2124,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592213</v>
+        <v>121592210</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,34 +2162,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594681</v>
+        <v>594660</v>
       </c>
       <c r="R15" t="n">
-        <v>7185598</v>
+        <v>7185655</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2236,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592193</v>
+        <v>121592222</v>
       </c>
       <c r="B16" t="n">
-        <v>74706</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,38 +2275,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594293</v>
+        <v>594343</v>
       </c>
       <c r="R16" t="n">
-        <v>7185910</v>
+        <v>7185457</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592194</v>
+        <v>121592203</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,34 +2396,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594293</v>
+        <v>594461</v>
       </c>
       <c r="R17" t="n">
-        <v>7185909</v>
+        <v>7185985</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592212</v>
+        <v>121592189</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,39 +2513,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594673</v>
+        <v>594269</v>
       </c>
       <c r="R18" t="n">
-        <v>7185646</v>
+        <v>7185866</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2577,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,10 +2609,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592211</v>
+        <v>121592202</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,34 +2625,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594658</v>
+        <v>594480</v>
       </c>
       <c r="R19" t="n">
-        <v>7185656</v>
+        <v>7186028</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,10 +2726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592192</v>
+        <v>121592211</v>
       </c>
       <c r="B20" t="n">
-        <v>74727</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,21 +2742,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594293</v>
+        <v>594658</v>
       </c>
       <c r="R20" t="n">
-        <v>7185910</v>
+        <v>7185656</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592219</v>
+        <v>121592202</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594709</v>
+        <v>594480</v>
       </c>
       <c r="R2" t="n">
-        <v>7185499</v>
+        <v>7186028</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592194</v>
+        <v>121592208</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594293</v>
+        <v>594557</v>
       </c>
       <c r="R3" t="n">
-        <v>7185909</v>
+        <v>7185802</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592208</v>
+        <v>121592212</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594557</v>
+        <v>594673</v>
       </c>
       <c r="R4" t="n">
-        <v>7185802</v>
+        <v>7185646</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592187</v>
+        <v>121592213</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594367</v>
+        <v>594681</v>
       </c>
       <c r="R5" t="n">
-        <v>7185583</v>
+        <v>7185598</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592205</v>
+        <v>121592210</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594475</v>
+        <v>594660</v>
       </c>
       <c r="R6" t="n">
-        <v>7185979</v>
+        <v>7185655</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592212</v>
+        <v>121592222</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,16 +1266,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1276,7 +1286,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1285,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594673</v>
+        <v>594343</v>
       </c>
       <c r="R7" t="n">
-        <v>7185646</v>
+        <v>7185457</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592193</v>
+        <v>121592187</v>
       </c>
       <c r="B8" t="n">
-        <v>74706</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,38 +1379,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594293</v>
+        <v>594367</v>
       </c>
       <c r="R8" t="n">
-        <v>7185910</v>
+        <v>7185583</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592220</v>
+        <v>121592192</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>74727</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,39 +1500,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594604</v>
+        <v>594293</v>
       </c>
       <c r="R9" t="n">
-        <v>7185461</v>
+        <v>7185910</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1596,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592190</v>
+        <v>121592211</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1626,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594270</v>
+        <v>594658</v>
       </c>
       <c r="R10" t="n">
-        <v>7185863</v>
+        <v>7185656</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592192</v>
+        <v>121592190</v>
       </c>
       <c r="B11" t="n">
-        <v>74727</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594293</v>
+        <v>594270</v>
       </c>
       <c r="R11" t="n">
-        <v>7185910</v>
+        <v>7185863</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592207</v>
+        <v>121592220</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,34 +1836,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594451</v>
+        <v>594604</v>
       </c>
       <c r="R12" t="n">
-        <v>7185924</v>
+        <v>7185461</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,7 +1937,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592213</v>
+        <v>121592205</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1962,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594681</v>
+        <v>594475</v>
       </c>
       <c r="R13" t="n">
-        <v>7185598</v>
+        <v>7185979</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592188</v>
+        <v>121592203</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,34 +2065,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594365</v>
+        <v>594461</v>
       </c>
       <c r="R14" t="n">
-        <v>7185581</v>
+        <v>7185985</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592210</v>
+        <v>121592194</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,39 +2182,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594660</v>
+        <v>594293</v>
       </c>
       <c r="R15" t="n">
-        <v>7185655</v>
+        <v>7185909</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592222</v>
+        <v>121592188</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,39 +2294,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594343</v>
+        <v>594365</v>
       </c>
       <c r="R16" t="n">
-        <v>7185457</v>
+        <v>7185581</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592203</v>
+        <v>121592207</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,39 +2406,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594461</v>
+        <v>594451</v>
       </c>
       <c r="R17" t="n">
-        <v>7185985</v>
+        <v>7185924</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2475,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2502,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592189</v>
+        <v>121592193</v>
       </c>
       <c r="B18" t="n">
-        <v>90746</v>
+        <v>74706</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,25 +2514,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2537,10 +2542,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594269</v>
+        <v>594293</v>
       </c>
       <c r="R18" t="n">
-        <v>7185866</v>
+        <v>7185910</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2577,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2587,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,10 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592202</v>
+        <v>121592219</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,39 +2630,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594480</v>
+        <v>594709</v>
       </c>
       <c r="R19" t="n">
-        <v>7186028</v>
+        <v>7185499</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,10 +2726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592211</v>
+        <v>121592189</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,21 +2742,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594658</v>
+        <v>594269</v>
       </c>
       <c r="R20" t="n">
-        <v>7185656</v>
+        <v>7185866</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592202</v>
+        <v>121592194</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594480</v>
+        <v>594293</v>
       </c>
       <c r="R2" t="n">
-        <v>7186028</v>
+        <v>7185909</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592208</v>
+        <v>121592189</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594557</v>
+        <v>594269</v>
       </c>
       <c r="R3" t="n">
-        <v>7185802</v>
+        <v>7185866</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592212</v>
+        <v>121592202</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594673</v>
+        <v>594480</v>
       </c>
       <c r="R4" t="n">
-        <v>7185646</v>
+        <v>7186028</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592213</v>
+        <v>121592211</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1061,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594681</v>
+        <v>594658</v>
       </c>
       <c r="R5" t="n">
-        <v>7185598</v>
+        <v>7185656</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592210</v>
+        <v>121592188</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594660</v>
+        <v>594365</v>
       </c>
       <c r="R6" t="n">
-        <v>7185655</v>
+        <v>7185581</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592222</v>
+        <v>121592190</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594343</v>
+        <v>594270</v>
       </c>
       <c r="R7" t="n">
-        <v>7185457</v>
+        <v>7185863</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1484,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592192</v>
+        <v>121592220</v>
       </c>
       <c r="B9" t="n">
-        <v>74727</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,34 +1485,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594293</v>
+        <v>594604</v>
       </c>
       <c r="R9" t="n">
-        <v>7185910</v>
+        <v>7185461</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592211</v>
+        <v>121592210</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,34 +1602,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594658</v>
+        <v>594660</v>
       </c>
       <c r="R10" t="n">
-        <v>7185656</v>
+        <v>7185655</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1708,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592190</v>
+        <v>121592213</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1748,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594270</v>
+        <v>594681</v>
       </c>
       <c r="R11" t="n">
-        <v>7185863</v>
+        <v>7185598</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1783,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592220</v>
+        <v>121592192</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>74727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594604</v>
+        <v>594293</v>
       </c>
       <c r="R12" t="n">
-        <v>7185461</v>
+        <v>7185910</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1900,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,7 +1927,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592205</v>
+        <v>121592207</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1977,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594475</v>
+        <v>594451</v>
       </c>
       <c r="R13" t="n">
-        <v>7185979</v>
+        <v>7185924</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2012,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592203</v>
+        <v>121592212</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,16 +2055,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2085,7 +2075,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2094,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594461</v>
+        <v>594673</v>
       </c>
       <c r="R14" t="n">
-        <v>7185985</v>
+        <v>7185646</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2129,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592194</v>
+        <v>121592193</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>74706</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,25 +2168,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2209,7 +2199,7 @@
         <v>594293</v>
       </c>
       <c r="R15" t="n">
-        <v>7185909</v>
+        <v>7185910</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2278,7 +2268,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592188</v>
+        <v>121592208</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2318,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594365</v>
+        <v>594557</v>
       </c>
       <c r="R16" t="n">
-        <v>7185581</v>
+        <v>7185802</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2353,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2363,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592207</v>
+        <v>121592203</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,34 +2396,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594451</v>
+        <v>594461</v>
       </c>
       <c r="R17" t="n">
-        <v>7185924</v>
+        <v>7185985</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2465,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592193</v>
+        <v>121592219</v>
       </c>
       <c r="B18" t="n">
-        <v>74706</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,25 +2509,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2542,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594293</v>
+        <v>594709</v>
       </c>
       <c r="R18" t="n">
-        <v>7185910</v>
+        <v>7185499</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2577,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,7 +2609,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592219</v>
+        <v>121592205</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2654,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594709</v>
+        <v>594475</v>
       </c>
       <c r="R19" t="n">
-        <v>7185499</v>
+        <v>7185979</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2689,7 +2684,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2699,7 +2694,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,10 +2721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592189</v>
+        <v>121592222</v>
       </c>
       <c r="B20" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,34 +2737,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594269</v>
+        <v>594343</v>
       </c>
       <c r="R20" t="n">
-        <v>7185866</v>
+        <v>7185457</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592194</v>
+        <v>121592211</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594293</v>
+        <v>594658</v>
       </c>
       <c r="R2" t="n">
-        <v>7185909</v>
+        <v>7185656</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592189</v>
+        <v>121592212</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>57381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594269</v>
+        <v>594673</v>
       </c>
       <c r="R3" t="n">
-        <v>7185866</v>
+        <v>7185646</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592202</v>
+        <v>121592207</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594480</v>
+        <v>594451</v>
       </c>
       <c r="R4" t="n">
-        <v>7186028</v>
+        <v>7185924</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592211</v>
+        <v>121592220</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594658</v>
+        <v>594604</v>
       </c>
       <c r="R5" t="n">
-        <v>7185656</v>
+        <v>7185461</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592188</v>
+        <v>121592210</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594365</v>
+        <v>594660</v>
       </c>
       <c r="R6" t="n">
-        <v>7185581</v>
+        <v>7185655</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592190</v>
+        <v>121592202</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594270</v>
+        <v>594480</v>
       </c>
       <c r="R7" t="n">
-        <v>7185863</v>
+        <v>7186028</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592187</v>
+        <v>121592190</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,39 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594367</v>
+        <v>594270</v>
       </c>
       <c r="R8" t="n">
-        <v>7185583</v>
+        <v>7185863</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592220</v>
+        <v>121592192</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>74740</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,39 +1495,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594604</v>
+        <v>594293</v>
       </c>
       <c r="R9" t="n">
-        <v>7185461</v>
+        <v>7185910</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592210</v>
+        <v>121592193</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>74719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,43 +1603,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594660</v>
+        <v>594293</v>
       </c>
       <c r="R10" t="n">
-        <v>7185655</v>
+        <v>7185910</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592213</v>
+        <v>121592203</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1719,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594681</v>
+        <v>594461</v>
       </c>
       <c r="R11" t="n">
-        <v>7185598</v>
+        <v>7185985</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592192</v>
+        <v>121592208</v>
       </c>
       <c r="B12" t="n">
-        <v>74727</v>
+        <v>78629</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594293</v>
+        <v>594557</v>
       </c>
       <c r="R12" t="n">
-        <v>7185910</v>
+        <v>7185802</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592207</v>
+        <v>121592194</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594451</v>
+        <v>594293</v>
       </c>
       <c r="R13" t="n">
-        <v>7185924</v>
+        <v>7185909</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592212</v>
+        <v>121592205</v>
       </c>
       <c r="B14" t="n">
-        <v>57373</v>
+        <v>78629</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,39 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594673</v>
+        <v>594475</v>
       </c>
       <c r="R14" t="n">
-        <v>7185646</v>
+        <v>7185979</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592193</v>
+        <v>121592213</v>
       </c>
       <c r="B15" t="n">
-        <v>74706</v>
+        <v>78629</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,25 +2168,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594293</v>
+        <v>594681</v>
       </c>
       <c r="R15" t="n">
-        <v>7185910</v>
+        <v>7185598</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592208</v>
+        <v>121592188</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594557</v>
+        <v>594365</v>
       </c>
       <c r="R16" t="n">
-        <v>7185802</v>
+        <v>7185581</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592203</v>
+        <v>121592222</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594461</v>
+        <v>594343</v>
       </c>
       <c r="R17" t="n">
-        <v>7185985</v>
+        <v>7185457</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,7 +2500,7 @@
         <v>121592219</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592205</v>
+        <v>121592189</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>90760</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,21 +2625,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594475</v>
+        <v>594269</v>
       </c>
       <c r="R19" t="n">
-        <v>7185979</v>
+        <v>7185866</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,10 +2721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592222</v>
+        <v>121592187</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594343</v>
+        <v>594367</v>
       </c>
       <c r="R20" t="n">
-        <v>7185457</v>
+        <v>7185583</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 39678-2024 artfynd.xlsx
+++ b/artfynd/A 39678-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592211</v>
+        <v>121592192</v>
       </c>
       <c r="B2" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594658</v>
+        <v>594293</v>
       </c>
       <c r="R2" t="n">
-        <v>7185656</v>
+        <v>7185910</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,55 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592212</v>
+        <v>121592188</v>
       </c>
       <c r="B3" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594673</v>
+        <v>594365</v>
       </c>
       <c r="R3" t="n">
-        <v>7185646</v>
+        <v>7185581</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,19 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592207</v>
+        <v>121592190</v>
       </c>
       <c r="B4" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -944,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594451</v>
+        <v>594270</v>
       </c>
       <c r="R4" t="n">
-        <v>7185924</v>
+        <v>7185863</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,55 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592220</v>
+        <v>121592194</v>
       </c>
       <c r="B5" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594604</v>
+        <v>594293</v>
       </c>
       <c r="R5" t="n">
-        <v>7185461</v>
+        <v>7185909</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,55 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592210</v>
+        <v>121592205</v>
       </c>
       <c r="B6" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594660</v>
+        <v>594475</v>
       </c>
       <c r="R6" t="n">
-        <v>7185655</v>
+        <v>7185979</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,55 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592202</v>
+        <v>121592207</v>
       </c>
       <c r="B7" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594480</v>
+        <v>594451</v>
       </c>
       <c r="R7" t="n">
-        <v>7186028</v>
+        <v>7185924</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,19 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592190</v>
+        <v>121592208</v>
       </c>
       <c r="B8" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1407,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594270</v>
+        <v>594557</v>
       </c>
       <c r="R8" t="n">
-        <v>7185863</v>
+        <v>7185802</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,37 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592192</v>
+        <v>121592211</v>
       </c>
       <c r="B9" t="n">
-        <v>74740</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594293</v>
+        <v>594658</v>
       </c>
       <c r="R9" t="n">
-        <v>7185910</v>
+        <v>7185656</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592193</v>
+        <v>121592213</v>
       </c>
       <c r="B10" t="n">
-        <v>74719</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594293</v>
+        <v>594681</v>
       </c>
       <c r="R10" t="n">
-        <v>7185910</v>
+        <v>7185598</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,55 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592203</v>
+        <v>121592219</v>
       </c>
       <c r="B11" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594461</v>
+        <v>594709</v>
       </c>
       <c r="R11" t="n">
-        <v>7185985</v>
+        <v>7185499</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1783,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,37 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592208</v>
+        <v>121592193</v>
       </c>
       <c r="B12" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594557</v>
+        <v>594293</v>
       </c>
       <c r="R12" t="n">
-        <v>7185802</v>
+        <v>7185910</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,50 +1852,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592194</v>
+        <v>121592212</v>
       </c>
       <c r="B13" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594293</v>
+        <v>594673</v>
       </c>
       <c r="R13" t="n">
-        <v>7185909</v>
+        <v>7185646</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,15 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592205</v>
+        <v>121592187</v>
       </c>
       <c r="B14" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,34 +1975,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594475</v>
+        <v>594367</v>
       </c>
       <c r="R14" t="n">
-        <v>7185979</v>
+        <v>7185583</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,15 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592213</v>
+        <v>121592202</v>
       </c>
       <c r="B15" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,34 +2087,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594681</v>
+        <v>594480</v>
       </c>
       <c r="R15" t="n">
-        <v>7185598</v>
+        <v>7186028</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,15 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592188</v>
+        <v>121592203</v>
       </c>
       <c r="B16" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,34 +2199,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594365</v>
+        <v>594461</v>
       </c>
       <c r="R16" t="n">
-        <v>7185581</v>
+        <v>7185985</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,15 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592222</v>
+        <v>121592209</v>
       </c>
       <c r="B17" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2331,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2425,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594343</v>
+        <v>594654</v>
       </c>
       <c r="R17" t="n">
-        <v>7185457</v>
+        <v>7185719</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,7 +2375,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2385,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,15 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592219</v>
+        <v>121592210</v>
       </c>
       <c r="B18" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,34 +2423,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594709</v>
+        <v>594660</v>
       </c>
       <c r="R18" t="n">
-        <v>7185499</v>
+        <v>7185655</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,15 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592189</v>
+        <v>121592220</v>
       </c>
       <c r="B19" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2625,34 +2535,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594269</v>
+        <v>594604</v>
       </c>
       <c r="R19" t="n">
-        <v>7185866</v>
+        <v>7185461</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2684,7 +2599,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2694,7 +2609,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,15 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592187</v>
+        <v>121592222</v>
       </c>
       <c r="B20" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594367</v>
+        <v>594343</v>
       </c>
       <c r="R20" t="n">
-        <v>7185583</v>
+        <v>7185457</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2801,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2811,7 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
